--- a/workpaper_templates/WP19_Div7A_Unfranked_Dividend_Calculation.xlsx
+++ b/workpaper_templates/WP19_Div7A_Unfranked_Dividend_Calculation.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,11 +57,17 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +102,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFC0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -189,6 +205,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -196,8 +242,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -564,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -679,15 +724,15 @@
           <t>Net assets (per balance sheet)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="B6" s="10" t="inlineStr"/>
+      <c r="C6" s="11" t="inlineStr"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -695,15 +740,15 @@
           <t>Less: Paid-up share capital</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="B7" s="10" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -711,15 +756,15 @@
           <t>Less: Non-commercial loans</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="B8" s="10" t="inlineStr"/>
+      <c r="C8" s="11" t="inlineStr"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -727,31 +772,34 @@
           <t>Less: Amounts owed to associates</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr"/>
-      <c r="C9" s="9" t="inlineStr"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="11" t="inlineStr"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Distributable surplus</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr"/>
-      <c r="C10" s="9" t="inlineStr"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="B10" s="13">
+        <f>B6-B7-B8-B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
     </row>
     <row r="11" ht="6" customHeight="1">
       <c r="A11" s="5" t="n"/>
@@ -798,15 +846,15 @@
           <t>Dividend amount</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="B14" s="11" t="inlineStr"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -814,15 +862,15 @@
           <t>Dividend date</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -830,15 +878,15 @@
           <t>Franking status</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="B16" s="11" t="inlineStr"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -846,15 +894,15 @@
           <t>Franking account balance</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="B17" s="11" t="inlineStr"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -862,15 +910,15 @@
           <t>Unfranked amount</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="B18" s="11" t="inlineStr"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
     </row>
     <row r="19" ht="6" customHeight="1">
       <c r="A19" s="5" t="n"/>
@@ -928,407 +976,517 @@
       <c r="J21" s="8" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr"/>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="9" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="A22" s="11" t="inlineStr"/>
+      <c r="B22" s="14" t="inlineStr"/>
+      <c r="C22" s="15" t="inlineStr"/>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="11" t="inlineStr"/>
+      <c r="F22" s="11" t="inlineStr"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="9" t="inlineStr"/>
-      <c r="C23" s="9" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="14" t="inlineStr"/>
+      <c r="C23" s="15" t="inlineStr"/>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
-      <c r="B24" s="9" t="inlineStr"/>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr"/>
-      <c r="E24" s="9" t="inlineStr"/>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="A24" s="11" t="inlineStr"/>
+      <c r="B24" s="14" t="inlineStr"/>
+      <c r="C24" s="15" t="inlineStr"/>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
-      <c r="B25" s="9" t="inlineStr"/>
-      <c r="C25" s="9" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="14" t="inlineStr"/>
+      <c r="C25" s="15" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="9" t="inlineStr"/>
-      <c r="C26" s="9" t="inlineStr"/>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="9" t="inlineStr"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
+      <c r="A26" s="11" t="inlineStr"/>
+      <c r="B26" s="14" t="inlineStr"/>
+      <c r="C26" s="15" t="inlineStr"/>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr"/>
+      <c r="F26" s="11" t="inlineStr"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="9" t="inlineStr"/>
-      <c r="B27" s="9" t="inlineStr"/>
-      <c r="C27" s="9" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="9" t="inlineStr"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="14" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr"/>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>SUM(B22:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>SUM(C22:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="13">
+        <f>SUM(D22:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="12" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29" ht="6" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>D.  TAX IMPLICATIONS FOR SHAREHOLDERS</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Shareholder</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Dividend Amount</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Franking Credits</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Grossed-up Amount</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Marginal Rate</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Estimated Tax</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Net Cash</t>
         </is>
       </c>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr"/>
-      <c r="F32" s="9" t="inlineStr"/>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
+      <c r="A32" s="11" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr"/>
+      <c r="C32" s="10" t="inlineStr"/>
+      <c r="D32" s="18">
+        <f>B32+C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="18">
+        <f>D32*E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>B32-F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="9" t="inlineStr"/>
-      <c r="B33" s="9" t="inlineStr"/>
-      <c r="C33" s="9" t="inlineStr"/>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="A33" s="11" t="inlineStr"/>
+      <c r="B33" s="10" t="inlineStr"/>
+      <c r="C33" s="10" t="inlineStr"/>
+      <c r="D33" s="18">
+        <f>B33+C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="15" t="inlineStr"/>
+      <c r="F33" s="18">
+        <f>D33*E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>B33-F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="9" t="inlineStr"/>
-      <c r="B34" s="9" t="inlineStr"/>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr"/>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
+      <c r="A34" s="11" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr"/>
+      <c r="C34" s="10" t="inlineStr"/>
+      <c r="D34" s="18">
+        <f>B34+C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="18">
+        <f>D34*E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>B34-F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="9" t="inlineStr"/>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr"/>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
+      <c r="A35" s="11" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr"/>
+      <c r="C35" s="10" t="inlineStr"/>
+      <c r="D35" s="18">
+        <f>B35+C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="15" t="inlineStr"/>
+      <c r="F35" s="18">
+        <f>D35*E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="18">
+        <f>B35-F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="9" t="inlineStr"/>
-      <c r="B36" s="9" t="inlineStr"/>
-      <c r="C36" s="9" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr"/>
-      <c r="F36" s="9" t="inlineStr"/>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="6" customHeight="1">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
+      <c r="A36" s="11" t="inlineStr"/>
+      <c r="B36" s="10" t="inlineStr"/>
+      <c r="C36" s="10" t="inlineStr"/>
+      <c r="D36" s="18">
+        <f>B36+C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="15" t="inlineStr"/>
+      <c r="F36" s="18">
+        <f>D36*E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="18">
+        <f>B36-F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="11" t="inlineStr"/>
+      <c r="B37" s="10" t="inlineStr"/>
+      <c r="C37" s="10" t="inlineStr"/>
+      <c r="D37" s="18">
+        <f>B37+C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="15" t="inlineStr"/>
+      <c r="F37" s="18">
+        <f>D37*E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="18">
+        <f>B37-F37</f>
+        <v/>
+      </c>
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B38" s="13">
+        <f>SUM(B32:B37)</f>
+        <v/>
+      </c>
+      <c r="C38" s="13">
+        <f>SUM(C32:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="13">
+        <f>SUM(D32:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="13">
+        <f>SUM(F32:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="13">
+        <f>SUM(G32:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="6" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>E.  CONCLUSION</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="9" t="inlineStr"/>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
-      <c r="J39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="11" t="n"/>
-    </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="11" t="n"/>
+      <c r="A41" s="19" t="inlineStr"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="21" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="9" t="inlineStr"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="11" t="n"/>
+      <c r="A42" s="19" t="inlineStr"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="21" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="6" customHeight="1">
-      <c r="A44" s="5" t="n"/>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="21" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="19" t="inlineStr"/>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="20" t="n"/>
+      <c r="I44" s="20" t="n"/>
+      <c r="J44" s="21" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="19" t="inlineStr"/>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="20" t="n"/>
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="20" t="n"/>
+      <c r="I45" s="20" t="n"/>
+      <c r="J45" s="21" t="n"/>
+    </row>
+    <row r="46" ht="6" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>SIGN-OFF</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B48" s="23" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>{{preparer}}</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n"/>
-      <c r="E46" s="15" t="n"/>
-      <c r="F46" s="13" t="inlineStr">
+      <c r="D48" s="25" t="n"/>
+      <c r="E48" s="25" t="n"/>
+      <c r="F48" s="23" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G48" s="24" t="inlineStr">
         <is>
           <t>{{date_prepared}}</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="H48" s="25" t="n"/>
+      <c r="I48" s="25" t="n"/>
+      <c r="J48" s="25" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>Reviewed by:</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Name:</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C49" s="24" t="inlineStr">
         <is>
           <t>{{reviewer}}</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="n"/>
-      <c r="F47" s="13" t="inlineStr">
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G49" s="24" t="inlineStr">
         <is>
           <t>{{date_reviewed}}</t>
         </is>
       </c>
-      <c r="H47" s="15" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="15" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="25" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr"/>
-      <c r="C48" s="15" t="n"/>
-      <c r="D48" s="15" t="n"/>
-      <c r="E48" s="15" t="n"/>
-      <c r="F48" s="15" t="n"/>
-      <c r="G48" s="15" t="n"/>
-      <c r="H48" s="15" t="n"/>
-      <c r="I48" s="15" t="n"/>
-      <c r="J48" s="15" t="n"/>
+      <c r="B50" s="25" t="inlineStr"/>
+      <c r="C50" s="25" t="n"/>
+      <c r="D50" s="25" t="n"/>
+      <c r="E50" s="25" t="n"/>
+      <c r="F50" s="25" t="n"/>
+      <c r="G50" s="25" t="n"/>
+      <c r="H50" s="25" t="n"/>
+      <c r="I50" s="25" t="n"/>
+      <c r="J50" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="G47:J47"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A43:J43"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="C48:E48"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A45:J45"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="C49:E49"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="G49:J49"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A42:J42"/>
-    <mergeCell ref="B48:J48"/>
-    <mergeCell ref="C47:E47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
